--- a/integration-tests/spreadsheet/files/sample-file-append.xlsx
+++ b/integration-tests/spreadsheet/files/sample-file-append.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10602"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hans/git/hop/integration-tests/spreadsheet/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050CA716-8987-3E4F-96C1-FF0DFFC13541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47920" yWindow="3960" windowWidth="20880" windowHeight="12860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47920" yWindow="3960" windowWidth="20880" windowHeight="12860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="34">
   <si>
     <t>column1</t>
   </si>
@@ -76,12 +76,73 @@
   </si>
   <si>
     <t>here</t>
+  </si>
+  <si>
+    <t>aa</t>
+  </si>
+  <si>
+    <t>dssdfd</t>
+  </si>
+  <si>
+    <t>bb</t>
+  </si>
+  <si>
+    <t>gfdsgdfs</t>
+  </si>
+  <si>
+    <t>cc</t>
+  </si>
+  <si>
+    <t>sfdgf</t>
+  </si>
+  <si>
+    <t>dd</t>
+  </si>
+  <si>
+    <t>sdfgfsd</t>
+  </si>
+  <si>
+    <t>ee</t>
+  </si>
+  <si>
+    <t>sdfgsfd</t>
+  </si>
+  <si>
+    <t>ff</t>
+  </si>
+  <si>
+    <t>sfgsfg</t>
+  </si>
+  <si>
+    <t>gg</t>
+  </si>
+  <si>
+    <t>fsdgdfs</t>
+  </si>
+  <si>
+    <t>hh</t>
+  </si>
+  <si>
+    <t>sfgfsdfg</t>
+  </si>
+  <si>
+    <t>ii</t>
+  </si>
+  <si>
+    <t>sdfg</t>
+  </si>
+  <si>
+    <t>jj</t>
+  </si>
+  <si>
+    <t>sfgffd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -418,43 +479,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="18.5" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="15.33203125"/>
+    <col min="3" max="3" customWidth="true" width="13.5"/>
+    <col min="4" max="4" customWidth="true" width="18.5"/>
+    <col min="5" max="5" customWidth="true" width="15.6640625"/>
+    <col min="6" max="6" customWidth="true" width="20.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" s="0">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -462,10 +523,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="A4" s="0">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -473,10 +534,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="0">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -484,10 +545,10 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="A6" s="0">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -495,10 +556,10 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="A7" s="0">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -506,10 +567,10 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="A8" s="0">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -517,10 +578,10 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="A9" s="0">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -528,14 +589,454 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="A10" s="0">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
